--- a/Pharma.xlsx
+++ b/Pharma.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\MetaModels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0DFD6C-E451-46EB-9565-B29CD5A19AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F809555-FC18-4666-A813-61D7ED17FE8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21060" xr2:uid="{6C82A67D-F730-478A-A6D2-74994D82605C}"/>
+    <workbookView xWindow="225" yWindow="3120" windowWidth="38175" windowHeight="15240" xr2:uid="{6C82A67D-F730-478A-A6D2-74994D82605C}"/>
   </bookViews>
   <sheets>
     <sheet name="Biotech" sheetId="1" r:id="rId1"/>
@@ -839,6 +839,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Main"/>
@@ -849,12 +850,12 @@
       <sheetData sheetId="0">
         <row r="2">
           <cell r="J2">
-            <v>99.2</v>
+            <v>87.86</v>
           </cell>
         </row>
         <row r="4">
           <cell r="J4">
-            <v>1995.0458208000002</v>
+            <v>1766.9831231400001</v>
           </cell>
         </row>
         <row r="5">
@@ -13955,11 +13956,11 @@
       </c>
       <c r="E6" s="2">
         <f>+[1]Main!$J$2</f>
-        <v>99.2</v>
+        <v>87.86</v>
       </c>
       <c r="F6" s="12">
         <f>+[1]Main!$J$4</f>
-        <v>1995.0458208000002</v>
+        <v>1766.9831231400001</v>
       </c>
       <c r="G6" s="12">
         <f>+[1]Main!$J$6-[1]Main!$J$5</f>
@@ -13967,7 +13968,7 @@
       </c>
       <c r="H6" s="12">
         <f>+F6+G6</f>
-        <v>2129.0778208000002</v>
+        <v>1901.01512314</v>
       </c>
       <c r="I6" s="13" t="s">
         <v>210</v>
